--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28424-2026 artfynd.xlsx
+++ b/artfynd/A 28424-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950345</v>
       </c>
       <c r="B2" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136950346</v>
       </c>
       <c r="B3" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
